--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137345870</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137348022</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137353756</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137348639</v>
       </c>
       <c r="B5" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137349184</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137347103</v>
       </c>
       <c r="B7" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137347841</v>
       </c>
       <c r="B8" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137348032</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137347446</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>137347988</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137345769</v>
       </c>
       <c r="B12" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137345791</v>
       </c>
       <c r="B13" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137345854</v>
       </c>
       <c r="B14" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137345912</v>
       </c>
       <c r="B15" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>137346095</v>
       </c>
       <c r="B16" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137347964</v>
       </c>
       <c r="B17" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137348114</v>
       </c>
       <c r="B18" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137348290</v>
       </c>
       <c r="B19" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137348560</v>
       </c>
       <c r="B20" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137349625</v>
       </c>
       <c r="B21" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137346574</v>
       </c>
       <c r="B22" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137345819</v>
       </c>
       <c r="B25" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137346136</v>
       </c>
       <c r="B26" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>137346814</v>
       </c>
       <c r="B27" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137347318</v>
       </c>
       <c r="B28" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137347397</v>
       </c>
       <c r="B29" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>137347459</v>
       </c>
       <c r="B30" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>137347638</v>
       </c>
       <c r="B31" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>137348340</v>
       </c>
       <c r="B32" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>137348887</v>
       </c>
       <c r="B33" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>137349204</v>
       </c>
       <c r="B34" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137349238</v>
       </c>
       <c r="B35" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137349435</v>
       </c>
       <c r="B36" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>137349579</v>
       </c>
       <c r="B37" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137349716</v>
       </c>
       <c r="B38" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>137345833</v>
       </c>
       <c r="B41" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137348019</v>
       </c>
       <c r="B42" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>137353762</v>
       </c>
       <c r="B43" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137345870</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137348022</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137353756</v>
       </c>
       <c r="B4" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137348639</v>
       </c>
       <c r="B5" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137349184</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137347103</v>
       </c>
       <c r="B7" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137347841</v>
       </c>
       <c r="B8" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137345769</v>
       </c>
       <c r="B12" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137345791</v>
       </c>
       <c r="B13" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137345854</v>
       </c>
       <c r="B14" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137345912</v>
       </c>
       <c r="B15" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>137346095</v>
       </c>
       <c r="B16" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137347964</v>
       </c>
       <c r="B17" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137348114</v>
       </c>
       <c r="B18" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137348290</v>
       </c>
       <c r="B19" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137348560</v>
       </c>
       <c r="B20" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137349625</v>
       </c>
       <c r="B21" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137346574</v>
       </c>
       <c r="B22" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137345819</v>
       </c>
       <c r="B25" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137346136</v>
       </c>
       <c r="B26" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>137346814</v>
       </c>
       <c r="B27" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137347318</v>
       </c>
       <c r="B28" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137347397</v>
       </c>
       <c r="B29" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>137347459</v>
       </c>
       <c r="B30" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>137347638</v>
       </c>
       <c r="B31" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>137348340</v>
       </c>
       <c r="B32" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>137348887</v>
       </c>
       <c r="B33" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>137349204</v>
       </c>
       <c r="B34" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137349238</v>
       </c>
       <c r="B35" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137349435</v>
       </c>
       <c r="B36" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>137349579</v>
       </c>
       <c r="B37" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137349716</v>
       </c>
       <c r="B38" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>137345833</v>
       </c>
       <c r="B41" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137348019</v>
       </c>
       <c r="B42" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>137353762</v>
       </c>
       <c r="B43" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137345870</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137348022</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137353756</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137348639</v>
       </c>
       <c r="B5" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137349184</v>
       </c>
       <c r="B6" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137347103</v>
       </c>
       <c r="B7" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137347841</v>
       </c>
       <c r="B8" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137348032</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137347446</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>137347988</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137345769</v>
       </c>
       <c r="B12" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137345791</v>
       </c>
       <c r="B13" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137345854</v>
       </c>
       <c r="B14" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137345912</v>
       </c>
       <c r="B15" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>137346095</v>
       </c>
       <c r="B16" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137347964</v>
       </c>
       <c r="B17" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137348114</v>
       </c>
       <c r="B18" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137348290</v>
       </c>
       <c r="B19" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137348560</v>
       </c>
       <c r="B20" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137349625</v>
       </c>
       <c r="B21" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137346574</v>
       </c>
       <c r="B22" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137345819</v>
       </c>
       <c r="B25" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137346136</v>
       </c>
       <c r="B26" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>137346814</v>
       </c>
       <c r="B27" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137347318</v>
       </c>
       <c r="B28" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137347397</v>
       </c>
       <c r="B29" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>137347459</v>
       </c>
       <c r="B30" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>137347638</v>
       </c>
       <c r="B31" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>137348340</v>
       </c>
       <c r="B32" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>137348887</v>
       </c>
       <c r="B33" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>137349204</v>
       </c>
       <c r="B34" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137349238</v>
       </c>
       <c r="B35" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137349435</v>
       </c>
       <c r="B36" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>137349579</v>
       </c>
       <c r="B37" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137349716</v>
       </c>
       <c r="B38" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>137345833</v>
       </c>
       <c r="B41" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137348019</v>
       </c>
       <c r="B42" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>137353762</v>
       </c>
       <c r="B43" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137345870</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137348022</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137353756</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137348639</v>
       </c>
       <c r="B5" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137349184</v>
       </c>
       <c r="B6" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137347103</v>
       </c>
       <c r="B7" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137347841</v>
       </c>
       <c r="B8" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137345769</v>
       </c>
       <c r="B12" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137345791</v>
       </c>
       <c r="B13" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137345854</v>
       </c>
       <c r="B14" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137345912</v>
       </c>
       <c r="B15" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>137346095</v>
       </c>
       <c r="B16" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137347964</v>
       </c>
       <c r="B17" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137348114</v>
       </c>
       <c r="B18" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137348290</v>
       </c>
       <c r="B19" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137348560</v>
       </c>
       <c r="B20" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137349625</v>
       </c>
       <c r="B21" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137346574</v>
       </c>
       <c r="B22" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137345819</v>
       </c>
       <c r="B25" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137346136</v>
       </c>
       <c r="B26" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>137346814</v>
       </c>
       <c r="B27" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137347318</v>
       </c>
       <c r="B28" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137347397</v>
       </c>
       <c r="B29" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>137347459</v>
       </c>
       <c r="B30" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>137347638</v>
       </c>
       <c r="B31" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>137348340</v>
       </c>
       <c r="B32" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>137348887</v>
       </c>
       <c r="B33" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>137349204</v>
       </c>
       <c r="B34" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137349238</v>
       </c>
       <c r="B35" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137349435</v>
       </c>
       <c r="B36" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>137349579</v>
       </c>
       <c r="B37" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137349716</v>
       </c>
       <c r="B38" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>137345833</v>
       </c>
       <c r="B41" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137348019</v>
       </c>
       <c r="B42" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>137353762</v>
       </c>
       <c r="B43" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137345870</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137348022</v>
       </c>
       <c r="B3" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137353756</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137348639</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137349184</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137347103</v>
       </c>
       <c r="B7" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137347841</v>
       </c>
       <c r="B8" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137345769</v>
       </c>
       <c r="B12" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137345791</v>
       </c>
       <c r="B13" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137345854</v>
       </c>
       <c r="B14" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137345912</v>
       </c>
       <c r="B15" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>137346095</v>
       </c>
       <c r="B16" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137347964</v>
       </c>
       <c r="B17" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137348114</v>
       </c>
       <c r="B18" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137348290</v>
       </c>
       <c r="B19" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137348560</v>
       </c>
       <c r="B20" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137349625</v>
       </c>
       <c r="B21" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137346574</v>
       </c>
       <c r="B22" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137345819</v>
       </c>
       <c r="B25" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137346136</v>
       </c>
       <c r="B26" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>137346814</v>
       </c>
       <c r="B27" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137347318</v>
       </c>
       <c r="B28" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137347397</v>
       </c>
       <c r="B29" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>137347459</v>
       </c>
       <c r="B30" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>137347638</v>
       </c>
       <c r="B31" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>137348340</v>
       </c>
       <c r="B32" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>137348887</v>
       </c>
       <c r="B33" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>137349204</v>
       </c>
       <c r="B34" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137349238</v>
       </c>
       <c r="B35" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137349435</v>
       </c>
       <c r="B36" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>137349579</v>
       </c>
       <c r="B37" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137349716</v>
       </c>
       <c r="B38" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>137345833</v>
       </c>
       <c r="B41" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137348019</v>
       </c>
       <c r="B42" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>137353762</v>
       </c>
       <c r="B43" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137345870</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137348022</v>
       </c>
       <c r="B3" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137353756</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137348639</v>
       </c>
       <c r="B5" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137349184</v>
       </c>
       <c r="B6" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137347103</v>
       </c>
       <c r="B7" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137347841</v>
       </c>
       <c r="B8" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137345769</v>
       </c>
       <c r="B12" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137345791</v>
       </c>
       <c r="B13" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137345854</v>
       </c>
       <c r="B14" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137345912</v>
       </c>
       <c r="B15" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>137346095</v>
       </c>
       <c r="B16" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137347964</v>
       </c>
       <c r="B17" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137348114</v>
       </c>
       <c r="B18" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137348290</v>
       </c>
       <c r="B19" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137348560</v>
       </c>
       <c r="B20" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137349625</v>
       </c>
       <c r="B21" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137346574</v>
       </c>
       <c r="B22" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137345819</v>
       </c>
       <c r="B25" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137346136</v>
       </c>
       <c r="B26" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>137346814</v>
       </c>
       <c r="B27" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137347318</v>
       </c>
       <c r="B28" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137347397</v>
       </c>
       <c r="B29" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>137347459</v>
       </c>
       <c r="B30" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>137347638</v>
       </c>
       <c r="B31" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>137348340</v>
       </c>
       <c r="B32" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>137348887</v>
       </c>
       <c r="B33" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>137349204</v>
       </c>
       <c r="B34" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137349238</v>
       </c>
       <c r="B35" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137349435</v>
       </c>
       <c r="B36" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>137349579</v>
       </c>
       <c r="B37" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137349716</v>
       </c>
       <c r="B38" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>137345833</v>
       </c>
       <c r="B41" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137348019</v>
       </c>
       <c r="B42" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>137353762</v>
       </c>
       <c r="B43" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 43032-2026 artfynd.xlsx
+++ b/artfynd/A 43032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137345870</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137348022</v>
       </c>
       <c r="B3" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137353756</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137348639</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137349184</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137347103</v>
       </c>
       <c r="B7" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137347841</v>
       </c>
       <c r="B8" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137348032</v>
       </c>
       <c r="B9" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137347446</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>137347988</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137345769</v>
       </c>
       <c r="B12" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137345791</v>
       </c>
       <c r="B13" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137345854</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137345912</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>137346095</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137347964</v>
       </c>
       <c r="B17" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137348114</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137348290</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137348560</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>137349625</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137346574</v>
       </c>
       <c r="B22" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>137345803</v>
       </c>
       <c r="B23" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137347186</v>
       </c>
       <c r="B24" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137345819</v>
       </c>
       <c r="B25" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137346136</v>
       </c>
       <c r="B26" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>137346814</v>
       </c>
       <c r="B27" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137347318</v>
       </c>
       <c r="B28" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137347397</v>
       </c>
       <c r="B29" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>137347459</v>
       </c>
       <c r="B30" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>137347638</v>
       </c>
       <c r="B31" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>137348340</v>
       </c>
       <c r="B32" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>137348887</v>
       </c>
       <c r="B33" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>137349204</v>
       </c>
       <c r="B34" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137349238</v>
       </c>
       <c r="B35" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137349435</v>
       </c>
       <c r="B36" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>137349579</v>
       </c>
       <c r="B37" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137349716</v>
       </c>
       <c r="B38" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>137347855</v>
       </c>
       <c r="B39" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137348131</v>
       </c>
       <c r="B40" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>137345833</v>
       </c>
       <c r="B41" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>137348019</v>
       </c>
       <c r="B42" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>137353762</v>
       </c>
       <c r="B43" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
